--- a/光伏配储项目/电价数据/2026/田心站.xlsx
+++ b/光伏配储项目/电价数据/2026/田心站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.5086000000000001</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38426</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.74256</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.57176</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.5801799999999999</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.5025500000000001</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.49484</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.43734</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45413</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.43042</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42204</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.41504</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.40838</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.39715</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.39734</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38476</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40117</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.42285</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41234</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35416</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39132</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.3848</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41676</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39193</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42049</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41373</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42371</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41207</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44281</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.34172</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.32864</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.27206</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.29563</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.30608</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.29663</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.30966</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.11594</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.09431999999999999</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.10264</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.08671</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.11261</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.03569</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.07873999999999999</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.09267</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.09509999999999999</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.06451999999999999</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.08984</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.03369</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>-0.02834</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.14202</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.21257</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.21995</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.21928</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.21117</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.05085</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>-0.0114</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.2228</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.11885</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.24347</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.2658</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.27963</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.24078</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.17883</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.25882</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.52451</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.41055</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.48513</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>0.7166399999999999</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.39261</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.60042</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.42736</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.43542</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.42018</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.57076</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.45126</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>0.6041</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>0.7905800000000001</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>0.6411100000000001</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.60588</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>0.73403</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>0.87097</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.41819</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.66127</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.58609</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>0.66528</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.48715</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.43374</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.62318</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.60012</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.47106</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.4805</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.40448</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41627</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42599</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32881</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.6885</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.15597</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.66973</v>
+      </c>
+      <c r="F118" t="n">
+        <v>0.73284</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.70716</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.50269</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.51764</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.5047200000000001</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.50443</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.487</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.4001</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.46898</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.37855</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.37966</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39137</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33649</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.37006</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35552</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.35623</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.37526</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.37499</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.35912</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.37987</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.41881</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.49489</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.57021</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.5529400000000001</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.42911</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.34283</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.3798</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.3479</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.33873</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.41278</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.50845</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.15704</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.29316</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.35518</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.06886</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.29848</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.30696</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.29217</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.32116</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.31585</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.33881</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.47587</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.74307</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.95431</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.32074</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.37178</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.37927</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.37929</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.3363</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.67173</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.47027</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.40232</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.16627</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.28674</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.28665</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.35065</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.34201</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.32291</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.47877</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.34419</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.33779</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.31923</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.29191</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.2327</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>0.24244</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>0.41399</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.39141</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>0.31032</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.38397</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.33679</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>0.49383</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>0.59751</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>0.51101</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>0.66792</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.6564099999999999</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.71377</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.45087</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.43071</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.755</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.44592</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.3315</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>0.5659999999999999</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.34545</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.42625</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.48199</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.43396</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.42744</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.39925</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.31658</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37541</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35452</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33472</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32141</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.50802</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.3493</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.40401</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.31721</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.38326</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.39903</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.3615</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38261</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36307</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.4276</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.44308</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.3356</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37074</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39659</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.3669</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.36773</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35624</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36179</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35219</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36761</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35961</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.38552</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39651</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47393</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.4433</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.43765</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34699</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.3941</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35312</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36657</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34705</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.20425</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.22428</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.20562</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.31629</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.19277</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.17128</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.26729</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.31659</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.31776</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.31925</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.34246</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.48171</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.40554</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.5642699999999999</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.31936</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.49435</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.41566</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.30801</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.17581</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.31494</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.27727</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.32293</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.31061</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.29377</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.29587</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.33867</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.30538</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.29266</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.37973</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.38669</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.39895</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.4035899999999999</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.4563</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.38097</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.43376</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>0.48686</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.36729</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.38329</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.33885</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.35447</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.5151</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.59882</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.5440700000000001</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.6046699999999999</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.32721</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.4525</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.41758</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.4714</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.39788</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.43619</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.43301</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.45244</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.43901</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.38935</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.36922</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.41335</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.39338</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.39306</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.39624</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36108</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34863</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34202</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31888</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.41069</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.38263</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.29093</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.40121</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.39713</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.40835</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.37485</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.36637</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.4045</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.40132</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.3787</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.44751</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.37323</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.3568</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.38004</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.36884</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.37141</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.34534</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.34342</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.34269</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.34275</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.34212</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.35506</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33924</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35101</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.39804</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.38913</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.36341</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.3886</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.35047</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.40551</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.43294</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.44457</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.35592</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.25607</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.34794</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.14739</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.2395</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.16993</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.34829</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.26481</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.16766</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.3021</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.5665</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.26419</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.37839</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.28838</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.07374</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.07371999999999999</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.09197</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.3165</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.3696</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.20084</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.21149</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.64998</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.07758</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.18067</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.29287</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.4588</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.41025</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.42498</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.29394</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.29375</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.35131</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.17129</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.34308</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.33753</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.32805</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.33599</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.3383</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.33785</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.37925</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.36872</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.37953</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.39979</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.48356</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.48197</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.52261</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.43028</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.40933</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.40854</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.43093</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.34517</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.36536</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.35145</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.351</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.32027</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32291</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.29308</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.29535</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31261</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.29983</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.29984</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.29505</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.33108</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.38197</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.35526</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.3385</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.30335</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.31141</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.3069</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.31814</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31777</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.3142</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.30681</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.32103</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31597</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.29192</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.29194</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.29246</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.29853</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.29357</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.2965</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31339</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31645</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32453</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32433</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33256</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32611</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.28252</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.26531</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.05262</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.06722</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.05259</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.05095</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.04481</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.06943000000000001</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.06342</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.06675</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>-0.02678</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>-0.04596</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>-0.01791</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>-0.02372</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>-0.01189</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>-0.01811</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>-0.02146</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>-0.02299</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>-0.0083</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.03687</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.04209</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>-0.01255</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.03638</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.03915</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.03857</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.04511</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>-0.01331</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>-0.01899</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.21931</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.06977</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.07917</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.05928</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>-0.0039</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.15601</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.0289</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.09186</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.29009</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.29171</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.29425</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31546</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33572</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33585</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.33555</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.38879</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.39302</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.38851</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.37727</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.3414700000000001</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.40028</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.4007</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.41017</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46791</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.35495</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39679</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.40048</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.418</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35515</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35816</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34465</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35508</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.35136</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.36806</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.6553600000000001</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.40123</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.44845</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.42527</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.42553</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.36029</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.35969</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.35759</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.33425</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.30932</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.3256</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.35652</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.35839</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.34748</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.34618</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.33535</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.31673</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.33095</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.33661</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.32381</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.30052</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.32403</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33565</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.33982</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.35093</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.35235</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.34405</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31657</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04338</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04699</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04578</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04622</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04622</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04622</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04545</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.044</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.03023</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>-0.03321</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.12378</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.008189999999999999</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.0077</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>-0.00284</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.03765</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04396</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04575</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04563</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04372</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04337</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.0455</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.0434</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.03657</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.04534000000000001</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04525999999999999</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04539</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04359</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04424</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>-0.02202</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>-0.0241</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04473</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04988</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.04742</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04795</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19969</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14268</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28987</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29459</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30448</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29976</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29486</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29275</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.2932</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29217</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29671</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29493</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.2687</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29376</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29797</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30851</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30369</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.3022</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.3143</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31834</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34753</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.34957</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34455</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.36659</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36504</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33561</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33056</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.31712</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31031</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.40489</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.35009</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32061</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.307</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31459</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.3013</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.2811</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29439</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29064</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28799</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.2808</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27112</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27085</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.28099</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17234</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.15858</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.1709</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14768</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15941</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15856</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23608</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21397</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22648</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26881</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28562</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29071</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31929</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.29065</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.2808</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.28099</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28039</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27056</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28088</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32231</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31011</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30489</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.31626</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.3093399999999999</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35889</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31622</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29731</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.38325</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.37979</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.42812</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.45638</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33178</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41843</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41526</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.38894</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40241</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30004</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30094</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29927</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29997</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15656</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29419</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31092</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31342</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31257</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32183</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34625</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30065</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33081</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38544</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.50766</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.62203</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.7853300000000001</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49797</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.78101</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92037</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49455</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.91391</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.8620800000000001</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.29572</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.3528</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.8866499999999999</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.63144</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18624</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.86834</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.5439299999999999</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.32999</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.03232</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.5299400000000001</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.79027</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.5319299999999999</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.77225</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.77698</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8766799999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87349</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49248</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39802</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.39902</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44917</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.20612</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87878</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55099</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62099</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.5381</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49743</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.4557</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42414</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43698</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.44989</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38795</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45266</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.41973</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.35199</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.3653</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.3848</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41499</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43408</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34402</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.39028</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.35076</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.33801</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.33111</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.34469</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.40349</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34699</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.45079</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.35387</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.40045</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.40085</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.58766</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.42893</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.59645</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.60333</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.69511</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.46788</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.41941</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.5821799999999999</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.45202</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.8844099999999999</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.6351</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.8446900000000001</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>0.82377</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.86173</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.3461</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.44206</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.33336</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.33289</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.30568</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.29446</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.4359</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.30837</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.2632</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.3103</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.3572</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.33289</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32076</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.33679</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.33732</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.3179</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.30622</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31911</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31983</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.34444</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.31493</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.31539</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.32032</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29582</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.31218</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.31385</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.31217</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.31665</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.31062</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.31561</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.32275</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.32396</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.32506</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.35463</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.34108</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.34058</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.33849</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.33076</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.33789</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.33588</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.41129</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.41395</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.45406</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.41633</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.39256</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.37601</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.35379</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32834</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.91908</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36108</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.46642</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.3715</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.41016</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.4673</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.38167</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.41099</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.36159</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.36621</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.34985</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.34804</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.38968</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33096</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35979</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.3462</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32323</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.40139</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.5022</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.35772</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38872</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.3440299999999999</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35147</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.35593</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37152</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35869</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36381</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31703</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31395</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33315</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.3387</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.33846</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.35024</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.31513</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.31204</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.30752</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.28881</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.29684</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.16411</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30352</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30856</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.33154</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.30645</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.32227</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.29866</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.26204</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.19895</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.27734</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.19342</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.31147</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.27849</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.31154</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.31187</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.35242</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.35805</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.31504</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.31213</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.32058</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.3078</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.31636</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.29565</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.31211</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.29215</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.30881</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.32125</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.31441</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.29007</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.34885</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.25569</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.35065</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32249</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.34808</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.33764</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.27654</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.35108</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.32944</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.34089</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.31044</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.35079</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.34113</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.38649</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.3542</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.44729</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.35064</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.41283</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.4233</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.35332</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.4509</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.34266</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.4215</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35935</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40286</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.40165</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.60024</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.35161</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.89127</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.36307</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.16607</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.70114</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.79216</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.66884</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.5855</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.45388</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.45148</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.5019400000000001</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.44102</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43923</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41603</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41386</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.42511</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.50362</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41385</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43514</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41472</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43527</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.39117</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.43021</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.45296</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39715</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.42446</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43637</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41385</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41377</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.40199</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.42575</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.40019</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.40454</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.49577</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.36351</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.34822</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.29684</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.36787</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.36879</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.3107200000000001</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.34165</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.30732</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.31094</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.30417</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.54234</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.36259</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.31012</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.24959</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.3475</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.11718</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.27256</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.26987</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.33652</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30074</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.262</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.25537</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.30666</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.28252</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.28463</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.28934</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.29181</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.3099</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.31307</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.32369</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.33148</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.31594</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.3409700000000001</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.34113</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.40418</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.40167</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.35118</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.36088</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.34055</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.33661</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.36812</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.34468</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.36342</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.36556</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.36273</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.34944</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.57141</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.46448</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.86951</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.46689</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.4382799999999999</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.37615</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.42965</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.38639</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.3692</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33387</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.34095</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.32901</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.32458</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.31828</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.4243</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.33955</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.34451</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.3408</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33507</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.32663</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.32987</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.32675</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.32537</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.32498</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.30994</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.32735</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.32589</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.31916</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.31523</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.32131</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.32123</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.30974</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.32471</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.3107</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.32253</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.32126</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.3932</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.32831</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.35094</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.40156</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.37648</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.35018</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.33824</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.35559</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.33211</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.33665</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.31892</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.28439</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.33368</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.30544</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.27529</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.28952</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.27563</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.2206</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.13707</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.14222</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.27957</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.15056</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.14172</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.1349</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.14074</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.13359</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.24197</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.13381</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.25099</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.25343</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.13245</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.0917</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.10512</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.10531</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.11626</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.13242</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.13674</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.27157</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.31561</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.32485</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.34294</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31843</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.35454</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.34614</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.35975</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34373</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.38046</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.34729</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.39916</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.3611</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.38554</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.45122</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.40064</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.39168</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.40238</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39799</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.45587</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.44108</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.44031</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.44528</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44432</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.40245</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.39045</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.3976</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.39142</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.35985</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.36039</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34839</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.34932</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.33946</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.54125</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.389</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.47042</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.42484</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41687</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.37106</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.38162</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.38028</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.39361</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.37986</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.37042</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.38131</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.36084</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.39234</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.37117</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.38145</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.35089</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.34787</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35586</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.3454100000000001</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.3407</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.34579</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.3407</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.34543</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.3571</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.3713</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.3815</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.36099</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.34071</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.34103</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.3409</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.32838</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.34265</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.34944</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.3616</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.29798</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31386</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.30889</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.29526</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.2829</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.27304</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.2673</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.19476</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.30946</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.24784</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.24238</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.27134</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30102</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.28855</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31809</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.31524</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.30879</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.3468</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.31339</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.29118</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.24251</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.31535</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.32462</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.30589</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.28603</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.31882</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.33546</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.33836</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.33429</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.32723</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.32735</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.31934</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.34237</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.35208</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.34566</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.3538</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.36686</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.4146</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.39207</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.37424</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.2615</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.34597</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.3809</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.35626</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.35795</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.35546</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.41625</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.32093</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.35034</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.36757</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.37008</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.36042</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.38137</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.38147</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.38618</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.35038</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.36084</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.34019</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36641</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.42039</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.3708</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.39418</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.38094</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35291</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.3502</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.36054</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35227</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.3421</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.34815</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.34608</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.34998</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.34676</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.34133</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.34233</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.34314</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.3386</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.33857</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.33978</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33114</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.34094</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.33461</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.35048</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.34596</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.36215</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.32099</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.33144</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.33986</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.32897</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.32487</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.33668</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.32667</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.28942</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.39662</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.36043</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.30903</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.39915</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.43871</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.32676</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.42711</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.33317</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.30187</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.37647</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.05894</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.33205</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.25153</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.2522</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.09279999999999999</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.22806</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.28514</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.2861</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.31269</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.33603</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.28492</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.29718</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.30938</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.30681</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.29455</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.34681</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.35312</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.34569</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.32908</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.4128</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.33582</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.34077</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.33902</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.35251</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.31502</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.38719</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.31848</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.32485</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.32339</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.33875</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.33179</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.43424</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.41533</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.6890499999999999</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.36149</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.37147</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.33388</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.32479</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.5078</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.21922</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.37978</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.30129</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.31123</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.32621</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.32576</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.30371</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.3166</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.30683</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.29231</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.3198</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.30503</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.32524</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.34647</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.33298</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.32659</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.33275</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.32899</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.32896</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.31919</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.32465</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.32953</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32514</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.32766</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.32915</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.32744</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.32812</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.32438</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.3325</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.32796</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.32159</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.32021</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.32338</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.32713</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.33224</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.33681</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.34726</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.3422</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.34267</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.33692</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.34035</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.32388</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.32341</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.3347</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.34432</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.34881</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.33511</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.32122</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.32399</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.32329</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32474</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.31957</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.34191</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.30626</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.34794</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.34544</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.31741</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.32954</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28375</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.32645</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.32044</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.32359</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.32737</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32986</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33494</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.33313</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.32833</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.32821</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.32073</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.32182</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.32145</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.3138</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.35115</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.3073</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.2972</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.32284</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.36343</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.34188</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.34485</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.33489</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.3505</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.35065</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.3507</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.36243</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.33249</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.33178</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.38306</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.46369</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.45572</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.4476</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.45468</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.44879</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.46015</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.39794</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.5224500000000001</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38695</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37205</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.45565</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.3554</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.38098</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.43962</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.36292</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.35259</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.35042</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.35063</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.35002</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.34008</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.35062</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.34954</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.3507</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.35161</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35121</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.35041</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.35018</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34964</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34651</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.36435</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.3473</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.37434</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.35015</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33783</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.33986</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.34041</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.3402</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.37018</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32475</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.33892</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.33986</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.35018</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.33722</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.34037</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.3454100000000001</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.33646</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.35009</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.3501</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33662</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.34089</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.32895</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.34926</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.34112</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.3325</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.33727</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.30949</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.3269</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.32877</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.3299</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.32676</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.31879</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.33075</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.32121</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.32108</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.33266</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32587</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.33262</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.32145</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37379</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32761</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.32319</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.31899</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.32602</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.33073</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.3285</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32191</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.32494</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.33133</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.33204</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.33313</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.33758</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34524</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.35934</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.33766</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.35516</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35428</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.36671</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.35022</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.36012</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34609</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.35937</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.35912</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36116</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.34906</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.38293</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.37977</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.38156</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.38533</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.47202</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.41183</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.37995</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.37592</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.6565800000000001</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.77762</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.45352</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.28136</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.45981</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.38906</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.35063</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.34781</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.35945</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.33993</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.34498</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32133</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.41138</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.37662</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.37149</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.36239</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.35953</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.3592</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.36236</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.35831</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.36084</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.35932</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35318</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.36033</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.36089</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35641</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35242</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35986</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.35983</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.36016</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.3474</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.37181</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35912</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35687</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.36042</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.36042</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.37969</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36623</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.3802</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35693</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35683</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35156</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35225</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35815</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.34979</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.33005</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.32401</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.33481</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.32875</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.26595</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.14832</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.30366</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.28652</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.28405</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.19805</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.25968</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.2782</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.3058999999999999</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.27956</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.2144</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.25288</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.28428</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.27613</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.28921</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.28933</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.30449</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.31052</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.32214</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.16215</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.29182</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.28809</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.34412</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.32199</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.33898</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.3346</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.33394</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.35045</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.3339</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.31497</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.33171</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.36286</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.34875</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.36262</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.36349</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.43841</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.39051</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.47195</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.69702</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.6525700000000001</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.66491</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.5494</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.8924299999999999</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.49473</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.8797</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.52716</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.52215</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.43254</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.42652</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.39014</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.50626</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.43198</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.42026</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.37927</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.37518</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36789</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.36068</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34511</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.49122</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.52949</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.48182</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.48672</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.41781</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.39836</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.4036</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.41106</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.40901</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.41747</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.39967</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.39484</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.41154</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.40934</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.39518</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.38859</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.42086</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.38907</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.41837</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.39151</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.40156</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.40134</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.41459</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.40132</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.4539</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.45202</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.56638</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.5051</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.4539</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.49035</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.45108</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.44776</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.35473</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.38483</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.40233</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.43971</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.42997</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.52242</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.43629</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.29861</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.33461</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.36838</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.4044</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.40065</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.32735</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.33885</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.29656</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.32455</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.3149</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.3237</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.35025</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.37312</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.62624</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.37101</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.34442</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.19085</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.28575</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.33675</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.34284</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.30703</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.3399</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.35832</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.33606</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.37683</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.36096</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.37288</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.35567</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.35899</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.35348</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.384</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.33809</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.41337</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.43758</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.49479</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.44035</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.5589299999999999</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>1.17369</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.6012000000000001</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.75054</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.77254</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>1.05066</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>1.2658</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.8135599999999999</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.58625</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.52691</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.83823</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.76891</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.6233200000000001</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.67169</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.4406600000000001</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.47267</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.48412</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.47884</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.47125</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.41834</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.5543400000000001</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.42903</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.44322</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.45724</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.43424</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.42437</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.44698</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.416</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.45707</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.3988</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.40588</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.39775</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38687</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.37859</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.37376</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.3604</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.3572</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36618</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.38095</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.3723</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.36104</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.36001</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36618</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.38746</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.39147</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.37961</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.36709</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36153</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35532</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37975</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.37259</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.38918</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.40087</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.39723</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38737</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35239</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.37138</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.34712</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.3420299999999999</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.34951</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.37961</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.18731</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.38519</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.33377</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.35249</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.36238</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.3527</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.40834</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.36581</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.46212</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.40291</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.47145</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.33447</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.32354</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.10749</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.18275</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.30554</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.30045</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32604</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.35656</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.3516</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.35067</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.35247</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.37464</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.38163</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.37608</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.38278</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.419</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.37313</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.4335</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.41644</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.41666</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.3839</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.37786</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.3886</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.39395</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.41187</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.41174</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34708</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.37364</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.3764</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.39802</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.36041</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.38024</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.3554</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.40108</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.38274</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.376</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.36225</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.39841</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.38341</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36793</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.33121</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.44722</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.36043</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.3957</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.39516</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.3556</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.3812</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.35257</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.38334</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.35772</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.3633</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.35984</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.35242</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.36391</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.34793</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.35168</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.35161</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.3442</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.33338</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.3420899999999999</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.34196</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.33741</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.34244</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.34747</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.3346</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.3325</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.33329</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.33364</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.33872</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.31936</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.31208</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.30545</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.3221</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.27049</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.32105</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.31443</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.3103399999999999</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.2292</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.28725</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.22842</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.2862</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.24798</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.24414</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.14345</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.29265</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.29787</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.3071</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.2471</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04383</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.25019</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.2772</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.16692</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.18567</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.27419</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.3137200000000001</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.29927</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.23309</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.25888</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.26268</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.2365</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.27744</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28506</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.28771</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.33317</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.33002</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.31203</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.35526</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.35021</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.35308</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.36261</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.35469</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.36297</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.332</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.3759</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.36412</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.34494</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.3107</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.36164</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.3592</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.3805</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.35585</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.37032</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.37182</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.37193</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.34619</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.36574</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.37944</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.34143</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.36449</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.3707</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.36273</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.34877</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.35008</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.34854</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.3503500000000001</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.35133</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.32221</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.32406</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.33785</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.34148</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.3434700000000001</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.33872</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.33287</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.32467</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.31981</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.31785</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.31204</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.3096</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.31447</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.31185</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.31251</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.31519</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.31488</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.31476</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.31083</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.31083</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.31325</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.30653</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.31032</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.31083</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.31121</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.31201</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.31537</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.29509</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.35388</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.3396</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.22661</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.29143</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.27224</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.01824</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00036</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.00754</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04965</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.1574</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.03143</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03965</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.04966</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.01492</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.0438</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.04192</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04879</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04848</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02423</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.03009</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04968</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>0.01306</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.04967</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04967</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04947</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.00198</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.29438</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04971</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.04931</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04967</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.02885</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.01329</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04966</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04976</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.03417</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.21497</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.28374</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.3033</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.27962</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.32484</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.32702</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.32934</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.3313</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.35348</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.36349</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.35788</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.36661</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.33634</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.32397</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.37881</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.37271</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.37501</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.36666</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.36052</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.37052</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.3672</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.40202</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.48543</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.38131</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.40369</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.3771600000000001</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.3815</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.37171</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.37239</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.40033</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.41938</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.40485</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.98898</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.96508</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.47688</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.598</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.4732</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.48757</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.56362</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.40478</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.41378</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.37875</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.43042</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.39175</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.40157</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.41825</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.37209</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.39376</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.43645</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.34768</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.41902</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.37538</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.41853</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.38208</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.39921</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.42279</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.44243</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.46751</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.43013</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.38097</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.3745</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.3829</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.46964</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>1.0734</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.94265</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.98372</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.36798</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.4298</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.20704</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.32407</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.36838</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.37251</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.35469</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.36766</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.28657</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.35074</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.37802</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.18553</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>0.18528</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.33923</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.32883</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.01465</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.31197</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.0071</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.36379</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.36621</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.34248</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.08443000000000001</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.34608</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.3475</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.3454700000000001</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.37087</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25396</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29162</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.27438</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.31301</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.32681</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.32781</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.3243</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.33565</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.3321</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.33462</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.32895</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.35405</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.37074</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.37452</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.33609</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.38485</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.38446</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.39755</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.37715</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.37376</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.36571</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>0.35916</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.35129</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.36851</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.35155</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.36248</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.37764</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.33786</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.33603</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.32849</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.32956</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.32865</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.33907</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.32393</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.35795</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.36062</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.25019</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.32697</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.32589</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.33622</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.334</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.33489</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.3457</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.33229</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.34999</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.35655</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.34919</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.33036</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.34628</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.4135</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.35468</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.33572</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.34083</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.33778</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.3443</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.37585</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.35456</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.36705</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.36021</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.49549</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.52127</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.39387</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.40713</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.32601</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.35092</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.31992</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.48135</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.38731</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.37253</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.39318</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.36321</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.43855</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.37603</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.36356</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.35469</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.43171</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.32221</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.30546</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.32101</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.32662</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.31049</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.14049</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.27431</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.26996</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30499</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.32684</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.32177</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.32063</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.34673</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.32944</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.29904</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31032</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.29087</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.3121</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.31826</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.32285</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.32741</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.33269</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32555</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.34866</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.34545</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.34652</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.34803</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.34751</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.35483</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.3348</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.35844</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.3506</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.33479</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.34926</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.33537</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.36249</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.36601</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.36508</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.34568</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.35818</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.39827</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.35808</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.36165</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.35532</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.35906</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.35043</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.36256</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.35175</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.31163</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.33147</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.32112</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.33056</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.33001</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.40578</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.33457</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.33446</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.34912</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.31947</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.32263</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.36123</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.33198</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.33249</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.33682</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.3606</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.34578</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.3784</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.34948</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.34039</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.33925</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.32653</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.32498</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.341</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34708</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.33205</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.34119</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.35482</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.32437</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.36929</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.35659</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.37014</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35999</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.35875</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.35502</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.3322</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.35334</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.34635</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.45792</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.31719</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.46919</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.41716</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.4918</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.37155</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.36315</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.35199</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.35177</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.30422</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.34325</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.33497</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.39079</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.34891</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.30678</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.33929</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.31386</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.32972</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.25481</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.32854</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.34461</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.34701</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32584</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.32385</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.27715</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.32958</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.3285</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.33122</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.32174</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.35111</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.34802</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.38769</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.38362</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.47201</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.4753</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.37288</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.37153</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.40999</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.44652</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.40226</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.39369</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.46969</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.35833</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.5748300000000001</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.37738</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.35023</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.38179</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.40076</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.37312</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.41528</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.34349</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.36917</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.3593</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.45887</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.40133</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.37237</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.40205</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.37969</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.23851</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.37293</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.35837</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.36873</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34697</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.4783</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.40156</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.4018</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.39243</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.38116</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.36075</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.37604</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.37441</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37926</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.37764</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.3697</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.36681</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.36156</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.35975</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.36079</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.36062</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.35565</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32748</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35644</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.3504</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.34858</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.3476</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.34971</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.36088</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.37062</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.40016</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.37531</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.36595</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.35809</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.35455</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.35007</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.35427</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.3872</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.38787</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.36451</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.33788</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.43103</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.37671</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.36972</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.35594</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.35545</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.30911</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.36328</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.2603</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.37495</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.35524</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.35653</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29291</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.30783</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.32436</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.3345</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.30723</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.31722</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.3378</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.34436</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.30782</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33275</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.33981</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.33624</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.29984</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.34386</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.34451</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.38155</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.37427</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.38031</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.36148</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.38545</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.41905</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.38422</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.39787</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.42608</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.42493</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.49467</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.57199</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.56284</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.439</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.56862</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.6272300000000001</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.49546</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.52262</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.56148</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.47136</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.6142000000000001</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.7394500000000001</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.70177</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.60765</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.5333600000000001</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.5327499999999999</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.398</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.44126</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.39619</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.37373</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.37727</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.36746</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.3729</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.30019</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.3701</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.37746</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.36613</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.36568</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.35264</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.34736</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.36873</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.35652</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.35023</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.3564</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.34022</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.40829</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.35731</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.34307</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.36474</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.3649</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.3599</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.35058</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.35414</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.35674</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.35778</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.34993</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.3689</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.38414</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.36899</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.38852</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.39924</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.37746</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.37245</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.37072</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.36726</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.40343</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.3558</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.37807</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.37918</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.33966</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.35873</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.34338</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.14278</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.25388</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.28213</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.05847</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.29995</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.31601</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.13428</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.02997</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.20301</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.15489</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>-0.00718</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.28478</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.25822</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.14692</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.05734</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.04309</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.06686</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.18318</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.07194</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.05515</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.15922</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.19176</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.31668</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.36186</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.36045</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.32806</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.35951</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.34828</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.35688</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.36397</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.3479100000000001</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.36073</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.34835</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.38055</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.36531</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.34713</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.3745</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.39124</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.4415</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.40843</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.3991</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.48501</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.45034</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.38028</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.39085</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.41609</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.38964</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.38432</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.42199</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.37442</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.42946</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.38337</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.37642</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.36143</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.35875</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.38765</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.34563</v>
+      </c>
+      <c r="C142" t="n">
+        <v>1.06808</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.39834</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.5762200000000001</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.52188</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.42183</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.39286</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.46594</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.41698</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.41504</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.40181</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.4019</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.39816</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.38757</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.38938</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.39309</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.39195</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.39953</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.39881</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.38778</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.38648</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.38664</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.38518</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.38931</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.37762</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.37354</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.39205</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.37836</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.39892</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.38438</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.36768</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.38013</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.38236</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.39309</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.3904</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.38252</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.36069</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.38514</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.37202</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.36984</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.36525</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.15082</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.0243</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.02348</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.02128</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.03118</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.27758</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.0478</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>-0.00153</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.01631</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.05173</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.01179</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.00727</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.02131</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.1607</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.30812</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.04861</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.34863</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.19239</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.37638</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.32614</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.32867</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.36534</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.33325</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.36962</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.34844</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.36604</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.40527</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.40356</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.44058</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.414</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.40705</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.36268</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.37316</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.39094</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.36533</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.36083</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.36636</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.42132</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.38226</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.38592</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.40144</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.37812</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.40233</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.36462</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.38264</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.34809</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.377</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.40577</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.37695</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.38393</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.35359</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.36869</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.37018</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.36963</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.37017</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.35231</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.48564</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.39924</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.39999</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.38393</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.3919</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.39199</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.38665</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.39232</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.40225</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.39025</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.38858</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.38341</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.38252</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.38301</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.38132</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.36271</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.3855</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.37897</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.38171</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.37987</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.37454</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.37036</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.37397</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.37557</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.37034</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.35347</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.37841</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.3727200000000001</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.3737799999999999</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.34255</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.33998</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.30658</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.18574</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.28977</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.3127</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.33251</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.15513</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.21243</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.12346</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.23132</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04697</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.05183</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.04981</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.04954</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.0498</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.04779</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.10425</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.03531</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.08391</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.13879</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.24318</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.28482</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.16461</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.38609</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.33123</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.16866</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.06134000000000001</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.32063</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.21349</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.15365</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.2974</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.26399</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.3509</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.34852</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.28313</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.33235</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.37594</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.37745</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.40512</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.37338</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.37753</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.38184</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.404</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.3583</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.35652</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.36754</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.36815</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.38995</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.38926</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.38717</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.35978</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.38684</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.41074</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.39539</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.3858</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.40773</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.47983</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.39648</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.39442</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.39156</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.39652</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.37686</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.38799</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.39335</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.39781</v>
       </c>
     </row>
   </sheetData>
